--- a/Libraries/Vehicle/Body/sm_car_data_Body2Axle.xlsx
+++ b/Libraries/Vehicle/Body/sm_car_data_Body2Axle.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Body\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DDAAB4-D130-451D-9B8E-101220BC00BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9FE389-44EA-4BDE-A5BE-0342DA47BF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3435" yWindow="1350" windowWidth="21555" windowHeight="11295" tabRatio="805" activeTab="2" xr2:uid="{06440896-8E0F-4240-830D-6ADD843B9DCF}"/>
+    <workbookView xWindow="1965" yWindow="1635" windowWidth="21600" windowHeight="11295" tabRatio="805" activeTab="2" xr2:uid="{06440896-8E0F-4240-830D-6ADD843B9DCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_Hamba" sheetId="2" r:id="rId1"/>
@@ -1190,13 +1190,13 @@
         <v>9</v>
       </c>
       <c r="F7" s="14">
-        <v>-1.2</v>
+        <v>-1.4379999999999999</v>
       </c>
       <c r="G7" s="14">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="H7" s="14">
-        <v>0.42249999999999999</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1286,7 +1286,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
       <c r="H12" s="14">
-        <v>1500</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1302,13 +1302,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>432</v>
+        <v>516</v>
       </c>
       <c r="G13" s="14">
-        <v>1922.7</v>
+        <v>3678</v>
       </c>
       <c r="H13" s="14">
-        <v>2066</v>
+        <v>4002</v>
       </c>
     </row>
   </sheetData>
